--- a/students/hip1.1 گلی ناس.xlsx
+++ b/students/hip1.1 گلی ناس.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0540575C-A2C4-475B-A5D4-3207429D0034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11760"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,12 +112,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -185,14 +186,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,23 +464,23 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" customWidth="1"/>
     <col min="5" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.85546875" customWidth="1"/>
+    <col min="7" max="7" width="41.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +503,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>111418</v>
       </c>
@@ -525,7 +524,7 @@
       </c>
       <c r="G2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>111419</v>
       </c>
@@ -538,11 +537,15 @@
       <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="E3" s="1">
+        <v>9195897392</v>
+      </c>
+      <c r="F3" s="1">
+        <v>9127417056</v>
+      </c>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>111423</v>
       </c>
@@ -563,7 +566,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>111200</v>
       </c>
@@ -584,7 +587,7 @@
       </c>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>111207</v>
       </c>
@@ -605,7 +608,7 @@
       </c>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>111515</v>
       </c>
@@ -626,7 +629,7 @@
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>111503</v>
       </c>
@@ -647,7 +650,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>111528</v>
       </c>
@@ -668,86 +671,84 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
         <v>111543</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="3">
         <v>9191437819</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>9122423985</v>
       </c>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>111610</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="D11" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11">
         <v>9120478825</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>9108464291</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>111676</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12">
         <v>9196733581</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>9929815491</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>111527</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13">
         <v>9127417023</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>9128412230</v>
       </c>
     </row>
